--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MICHIGAN_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MICHIGAN_2010.xlsx
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C127">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C453">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C489">
